--- a/Tratamento/src/Dados_limpos/novos/limpo_petz_20260708_205654.xlsx
+++ b/Tratamento/src/Dados_limpos/novos/limpo_petz_20260708_205654.xlsx
@@ -5820,7 +5820,7 @@
       </c>
       <c r="P73" t="inlineStr">
         <is>
-          <t>transdermal</t>
+          <t>plus</t>
         </is>
       </c>
     </row>
@@ -6120,7 +6120,7 @@
       </c>
       <c r="P77" t="inlineStr">
         <is>
-          <t>transdermal</t>
+          <t>plus</t>
         </is>
       </c>
     </row>
@@ -6274,7 +6274,7 @@
       </c>
       <c r="P79" t="inlineStr">
         <is>
-          <t>transdermal</t>
+          <t>plus</t>
         </is>
       </c>
     </row>
@@ -8554,7 +8554,7 @@
       </c>
       <c r="P110" t="inlineStr">
         <is>
-          <t>spot</t>
+          <t>spoton</t>
         </is>
       </c>
     </row>
@@ -8630,7 +8630,7 @@
       </c>
       <c r="P111" t="inlineStr">
         <is>
-          <t>spot</t>
+          <t>spoton</t>
         </is>
       </c>
     </row>
@@ -8706,7 +8706,7 @@
       </c>
       <c r="P112" t="inlineStr">
         <is>
-          <t>spot</t>
+          <t>spoton</t>
         </is>
       </c>
     </row>

--- a/Tratamento/src/Dados_limpos/novos/limpo_petz_20260708_205654.xlsx
+++ b/Tratamento/src/Dados_limpos/novos/limpo_petz_20260708_205654.xlsx
@@ -5820,7 +5820,7 @@
       </c>
       <c r="P73" t="inlineStr">
         <is>
-          <t>plus</t>
+          <t>transdermal</t>
         </is>
       </c>
     </row>
@@ -6120,7 +6120,7 @@
       </c>
       <c r="P77" t="inlineStr">
         <is>
-          <t>plus</t>
+          <t>transdermal</t>
         </is>
       </c>
     </row>
@@ -6274,7 +6274,7 @@
       </c>
       <c r="P79" t="inlineStr">
         <is>
-          <t>plus</t>
+          <t>transdermal</t>
         </is>
       </c>
     </row>
@@ -8554,7 +8554,7 @@
       </c>
       <c r="P110" t="inlineStr">
         <is>
-          <t>spoton</t>
+          <t>spot</t>
         </is>
       </c>
     </row>
@@ -8630,7 +8630,7 @@
       </c>
       <c r="P111" t="inlineStr">
         <is>
-          <t>spoton</t>
+          <t>spot</t>
         </is>
       </c>
     </row>
@@ -8706,7 +8706,7 @@
       </c>
       <c r="P112" t="inlineStr">
         <is>
-          <t>spoton</t>
+          <t>spot</t>
         </is>
       </c>
     </row>

--- a/Tratamento/src/Dados_limpos/novos/limpo_petz_20260708_205654.xlsx
+++ b/Tratamento/src/Dados_limpos/novos/limpo_petz_20260708_205654.xlsx
@@ -5820,7 +5820,7 @@
       </c>
       <c r="P73" t="inlineStr">
         <is>
-          <t>transdermal</t>
+          <t>plus</t>
         </is>
       </c>
     </row>
@@ -6120,7 +6120,7 @@
       </c>
       <c r="P77" t="inlineStr">
         <is>
-          <t>transdermal</t>
+          <t>plus</t>
         </is>
       </c>
     </row>
@@ -6274,7 +6274,7 @@
       </c>
       <c r="P79" t="inlineStr">
         <is>
-          <t>transdermal</t>
+          <t>plus</t>
         </is>
       </c>
     </row>
@@ -6492,7 +6492,7 @@
       </c>
       <c r="P82" t="inlineStr">
         <is>
-          <t>topspot</t>
+          <t>spot</t>
         </is>
       </c>
     </row>
@@ -6566,7 +6566,7 @@
       </c>
       <c r="P83" t="inlineStr">
         <is>
-          <t>topspot</t>
+          <t>spot</t>
         </is>
       </c>
     </row>
@@ -7096,7 +7096,7 @@
       </c>
       <c r="P90" t="inlineStr">
         <is>
-          <t>topspot</t>
+          <t>spot</t>
         </is>
       </c>
     </row>
@@ -7170,7 +7170,7 @@
       </c>
       <c r="P91" t="inlineStr">
         <is>
-          <t>topspot</t>
+          <t>spot</t>
         </is>
       </c>
     </row>
@@ -8554,7 +8554,7 @@
       </c>
       <c r="P110" t="inlineStr">
         <is>
-          <t>spot</t>
+          <t>spoton</t>
         </is>
       </c>
     </row>
@@ -8630,7 +8630,7 @@
       </c>
       <c r="P111" t="inlineStr">
         <is>
-          <t>spot</t>
+          <t>spoton</t>
         </is>
       </c>
     </row>
@@ -8706,7 +8706,7 @@
       </c>
       <c r="P112" t="inlineStr">
         <is>
-          <t>spot</t>
+          <t>spoton</t>
         </is>
       </c>
     </row>

--- a/Tratamento/src/Dados_limpos/novos/limpo_petz_20260708_205654.xlsx
+++ b/Tratamento/src/Dados_limpos/novos/limpo_petz_20260708_205654.xlsx
@@ -8554,7 +8554,7 @@
       </c>
       <c r="P110" t="inlineStr">
         <is>
-          <t>spot</t>
+          <t>spoton</t>
         </is>
       </c>
     </row>
@@ -8630,7 +8630,7 @@
       </c>
       <c r="P111" t="inlineStr">
         <is>
-          <t>spot</t>
+          <t>spoton</t>
         </is>
       </c>
     </row>
@@ -8706,7 +8706,7 @@
       </c>
       <c r="P112" t="inlineStr">
         <is>
-          <t>spot</t>
+          <t>spoton</t>
         </is>
       </c>
     </row>

--- a/Tratamento/src/Dados_limpos/novos/limpo_petz_20260708_205654.xlsx
+++ b/Tratamento/src/Dados_limpos/novos/limpo_petz_20260708_205654.xlsx
@@ -5820,7 +5820,7 @@
       </c>
       <c r="P73" t="inlineStr">
         <is>
-          <t>transdermal</t>
+          <t>plus</t>
         </is>
       </c>
     </row>
@@ -6120,7 +6120,7 @@
       </c>
       <c r="P77" t="inlineStr">
         <is>
-          <t>transdermal</t>
+          <t>plus</t>
         </is>
       </c>
     </row>
@@ -6274,7 +6274,7 @@
       </c>
       <c r="P79" t="inlineStr">
         <is>
-          <t>transdermal</t>
+          <t>plus</t>
         </is>
       </c>
     </row>
@@ -6492,7 +6492,7 @@
       </c>
       <c r="P82" t="inlineStr">
         <is>
-          <t>spot</t>
+          <t>topspot</t>
         </is>
       </c>
     </row>
@@ -6566,7 +6566,7 @@
       </c>
       <c r="P83" t="inlineStr">
         <is>
-          <t>spot</t>
+          <t>topspot</t>
         </is>
       </c>
     </row>
@@ -7096,7 +7096,7 @@
       </c>
       <c r="P90" t="inlineStr">
         <is>
-          <t>spot</t>
+          <t>topspot</t>
         </is>
       </c>
     </row>
@@ -7170,7 +7170,7 @@
       </c>
       <c r="P91" t="inlineStr">
         <is>
-          <t>spot</t>
+          <t>topspot</t>
         </is>
       </c>
     </row>

--- a/Tratamento/src/Dados_limpos/novos/limpo_petz_20260708_205654.xlsx
+++ b/Tratamento/src/Dados_limpos/novos/limpo_petz_20260708_205654.xlsx
@@ -6492,7 +6492,7 @@
       </c>
       <c r="P82" t="inlineStr">
         <is>
-          <t>topspot</t>
+          <t>spot</t>
         </is>
       </c>
     </row>
@@ -6566,7 +6566,7 @@
       </c>
       <c r="P83" t="inlineStr">
         <is>
-          <t>topspot</t>
+          <t>spot</t>
         </is>
       </c>
     </row>
@@ -7096,7 +7096,7 @@
       </c>
       <c r="P90" t="inlineStr">
         <is>
-          <t>topspot</t>
+          <t>spot</t>
         </is>
       </c>
     </row>
@@ -7170,7 +7170,7 @@
       </c>
       <c r="P91" t="inlineStr">
         <is>
-          <t>topspot</t>
+          <t>spot</t>
         </is>
       </c>
     </row>
@@ -8554,7 +8554,7 @@
       </c>
       <c r="P110" t="inlineStr">
         <is>
-          <t>spoton</t>
+          <t>spot</t>
         </is>
       </c>
     </row>
@@ -8630,7 +8630,7 @@
       </c>
       <c r="P111" t="inlineStr">
         <is>
-          <t>spoton</t>
+          <t>spot</t>
         </is>
       </c>
     </row>
@@ -8706,7 +8706,7 @@
       </c>
       <c r="P112" t="inlineStr">
         <is>
-          <t>spoton</t>
+          <t>spot</t>
         </is>
       </c>
     </row>

--- a/Tratamento/src/Dados_limpos/novos/limpo_petz_20260708_205654.xlsx
+++ b/Tratamento/src/Dados_limpos/novos/limpo_petz_20260708_205654.xlsx
@@ -6492,7 +6492,7 @@
       </c>
       <c r="P82" t="inlineStr">
         <is>
-          <t>spot</t>
+          <t>topspot</t>
         </is>
       </c>
     </row>
@@ -6566,7 +6566,7 @@
       </c>
       <c r="P83" t="inlineStr">
         <is>
-          <t>spot</t>
+          <t>topspot</t>
         </is>
       </c>
     </row>
@@ -7096,7 +7096,7 @@
       </c>
       <c r="P90" t="inlineStr">
         <is>
-          <t>spot</t>
+          <t>topspot</t>
         </is>
       </c>
     </row>
@@ -7170,7 +7170,7 @@
       </c>
       <c r="P91" t="inlineStr">
         <is>
-          <t>spot</t>
+          <t>topspot</t>
         </is>
       </c>
     </row>

--- a/Tratamento/src/Dados_limpos/novos/limpo_petz_20260708_205654.xlsx
+++ b/Tratamento/src/Dados_limpos/novos/limpo_petz_20260708_205654.xlsx
@@ -5820,7 +5820,7 @@
       </c>
       <c r="P73" t="inlineStr">
         <is>
-          <t>plus</t>
+          <t>transdermal</t>
         </is>
       </c>
     </row>
@@ -6120,7 +6120,7 @@
       </c>
       <c r="P77" t="inlineStr">
         <is>
-          <t>plus</t>
+          <t>transdermal</t>
         </is>
       </c>
     </row>
@@ -6274,7 +6274,7 @@
       </c>
       <c r="P79" t="inlineStr">
         <is>
-          <t>plus</t>
+          <t>transdermal</t>
         </is>
       </c>
     </row>
@@ -6492,7 +6492,7 @@
       </c>
       <c r="P82" t="inlineStr">
         <is>
-          <t>topspot</t>
+          <t>spot</t>
         </is>
       </c>
     </row>
@@ -6566,7 +6566,7 @@
       </c>
       <c r="P83" t="inlineStr">
         <is>
-          <t>topspot</t>
+          <t>spot</t>
         </is>
       </c>
     </row>
@@ -7096,7 +7096,7 @@
       </c>
       <c r="P90" t="inlineStr">
         <is>
-          <t>topspot</t>
+          <t>spot</t>
         </is>
       </c>
     </row>
@@ -7170,7 +7170,7 @@
       </c>
       <c r="P91" t="inlineStr">
         <is>
-          <t>topspot</t>
+          <t>spot</t>
         </is>
       </c>
     </row>

--- a/Tratamento/src/Dados_limpos/novos/limpo_petz_20260708_205654.xlsx
+++ b/Tratamento/src/Dados_limpos/novos/limpo_petz_20260708_205654.xlsx
@@ -6492,7 +6492,7 @@
       </c>
       <c r="P82" t="inlineStr">
         <is>
-          <t>topspot</t>
+          <t>spot</t>
         </is>
       </c>
     </row>
@@ -6566,7 +6566,7 @@
       </c>
       <c r="P83" t="inlineStr">
         <is>
-          <t>topspot</t>
+          <t>spot</t>
         </is>
       </c>
     </row>
@@ -7096,7 +7096,7 @@
       </c>
       <c r="P90" t="inlineStr">
         <is>
-          <t>topspot</t>
+          <t>spot</t>
         </is>
       </c>
     </row>
@@ -7170,7 +7170,7 @@
       </c>
       <c r="P91" t="inlineStr">
         <is>
-          <t>topspot</t>
+          <t>spot</t>
         </is>
       </c>
     </row>

--- a/Tratamento/src/Dados_limpos/novos/limpo_petz_20260708_205654.xlsx
+++ b/Tratamento/src/Dados_limpos/novos/limpo_petz_20260708_205654.xlsx
@@ -5820,7 +5820,7 @@
       </c>
       <c r="P73" t="inlineStr">
         <is>
-          <t>transdermal</t>
+          <t>plus</t>
         </is>
       </c>
     </row>
@@ -6120,7 +6120,7 @@
       </c>
       <c r="P77" t="inlineStr">
         <is>
-          <t>transdermal</t>
+          <t>plus</t>
         </is>
       </c>
     </row>
@@ -6274,7 +6274,7 @@
       </c>
       <c r="P79" t="inlineStr">
         <is>
-          <t>transdermal</t>
+          <t>plus</t>
         </is>
       </c>
     </row>

--- a/Tratamento/src/Dados_limpos/novos/limpo_petz_20260708_205654.xlsx
+++ b/Tratamento/src/Dados_limpos/novos/limpo_petz_20260708_205654.xlsx
@@ -6492,7 +6492,7 @@
       </c>
       <c r="P82" t="inlineStr">
         <is>
-          <t>spot</t>
+          <t>topspot</t>
         </is>
       </c>
     </row>
@@ -6566,7 +6566,7 @@
       </c>
       <c r="P83" t="inlineStr">
         <is>
-          <t>spot</t>
+          <t>topspot</t>
         </is>
       </c>
     </row>
@@ -7096,7 +7096,7 @@
       </c>
       <c r="P90" t="inlineStr">
         <is>
-          <t>spot</t>
+          <t>topspot</t>
         </is>
       </c>
     </row>
@@ -7170,7 +7170,7 @@
       </c>
       <c r="P91" t="inlineStr">
         <is>
-          <t>spot</t>
+          <t>topspot</t>
         </is>
       </c>
     </row>
@@ -8554,7 +8554,7 @@
       </c>
       <c r="P110" t="inlineStr">
         <is>
-          <t>spot</t>
+          <t>spoton</t>
         </is>
       </c>
     </row>
@@ -8630,7 +8630,7 @@
       </c>
       <c r="P111" t="inlineStr">
         <is>
-          <t>spot</t>
+          <t>spoton</t>
         </is>
       </c>
     </row>
@@ -8706,7 +8706,7 @@
       </c>
       <c r="P112" t="inlineStr">
         <is>
-          <t>spot</t>
+          <t>spoton</t>
         </is>
       </c>
     </row>

--- a/Tratamento/src/Dados_limpos/novos/limpo_petz_20260708_205654.xlsx
+++ b/Tratamento/src/Dados_limpos/novos/limpo_petz_20260708_205654.xlsx
@@ -6492,7 +6492,7 @@
       </c>
       <c r="P82" t="inlineStr">
         <is>
-          <t>spot</t>
+          <t>topspot</t>
         </is>
       </c>
     </row>
@@ -6566,7 +6566,7 @@
       </c>
       <c r="P83" t="inlineStr">
         <is>
-          <t>spot</t>
+          <t>topspot</t>
         </is>
       </c>
     </row>
@@ -7096,7 +7096,7 @@
       </c>
       <c r="P90" t="inlineStr">
         <is>
-          <t>spot</t>
+          <t>topspot</t>
         </is>
       </c>
     </row>
@@ -7170,7 +7170,7 @@
       </c>
       <c r="P91" t="inlineStr">
         <is>
-          <t>spot</t>
+          <t>topspot</t>
         </is>
       </c>
     </row>
@@ -8554,7 +8554,7 @@
       </c>
       <c r="P110" t="inlineStr">
         <is>
-          <t>spoton</t>
+          <t>spot</t>
         </is>
       </c>
     </row>
@@ -8630,7 +8630,7 @@
       </c>
       <c r="P111" t="inlineStr">
         <is>
-          <t>spoton</t>
+          <t>spot</t>
         </is>
       </c>
     </row>
@@ -8706,7 +8706,7 @@
       </c>
       <c r="P112" t="inlineStr">
         <is>
-          <t>spoton</t>
+          <t>spot</t>
         </is>
       </c>
     </row>

--- a/Tratamento/src/Dados_limpos/novos/limpo_petz_20260708_205654.xlsx
+++ b/Tratamento/src/Dados_limpos/novos/limpo_petz_20260708_205654.xlsx
@@ -6492,7 +6492,7 @@
       </c>
       <c r="P82" t="inlineStr">
         <is>
-          <t>topspot</t>
+          <t>spot</t>
         </is>
       </c>
     </row>
@@ -6566,7 +6566,7 @@
       </c>
       <c r="P83" t="inlineStr">
         <is>
-          <t>topspot</t>
+          <t>spot</t>
         </is>
       </c>
     </row>
@@ -7096,7 +7096,7 @@
       </c>
       <c r="P90" t="inlineStr">
         <is>
-          <t>topspot</t>
+          <t>spot</t>
         </is>
       </c>
     </row>
@@ -7170,7 +7170,7 @@
       </c>
       <c r="P91" t="inlineStr">
         <is>
-          <t>topspot</t>
+          <t>spot</t>
         </is>
       </c>
     </row>
@@ -8554,7 +8554,7 @@
       </c>
       <c r="P110" t="inlineStr">
         <is>
-          <t>spot</t>
+          <t>spoton</t>
         </is>
       </c>
     </row>
@@ -8630,7 +8630,7 @@
       </c>
       <c r="P111" t="inlineStr">
         <is>
-          <t>spot</t>
+          <t>spoton</t>
         </is>
       </c>
     </row>
@@ -8706,7 +8706,7 @@
       </c>
       <c r="P112" t="inlineStr">
         <is>
-          <t>spot</t>
+          <t>spoton</t>
         </is>
       </c>
     </row>

--- a/Tratamento/src/Dados_limpos/novos/limpo_petz_20260708_205654.xlsx
+++ b/Tratamento/src/Dados_limpos/novos/limpo_petz_20260708_205654.xlsx
@@ -5820,7 +5820,7 @@
       </c>
       <c r="P73" t="inlineStr">
         <is>
-          <t>transdermal</t>
+          <t>plus</t>
         </is>
       </c>
     </row>
@@ -6120,7 +6120,7 @@
       </c>
       <c r="P77" t="inlineStr">
         <is>
-          <t>transdermal</t>
+          <t>plus</t>
         </is>
       </c>
     </row>
@@ -6274,7 +6274,7 @@
       </c>
       <c r="P79" t="inlineStr">
         <is>
-          <t>transdermal</t>
+          <t>plus</t>
         </is>
       </c>
     </row>
@@ -6492,7 +6492,7 @@
       </c>
       <c r="P82" t="inlineStr">
         <is>
-          <t>spot</t>
+          <t>topspot</t>
         </is>
       </c>
     </row>
@@ -6566,7 +6566,7 @@
       </c>
       <c r="P83" t="inlineStr">
         <is>
-          <t>spot</t>
+          <t>topspot</t>
         </is>
       </c>
     </row>
@@ -7096,7 +7096,7 @@
       </c>
       <c r="P90" t="inlineStr">
         <is>
-          <t>spot</t>
+          <t>topspot</t>
         </is>
       </c>
     </row>
@@ -7170,7 +7170,7 @@
       </c>
       <c r="P91" t="inlineStr">
         <is>
-          <t>spot</t>
+          <t>topspot</t>
         </is>
       </c>
     </row>
@@ -8554,7 +8554,7 @@
       </c>
       <c r="P110" t="inlineStr">
         <is>
-          <t>spoton</t>
+          <t>spot</t>
         </is>
       </c>
     </row>
@@ -8630,7 +8630,7 @@
       </c>
       <c r="P111" t="inlineStr">
         <is>
-          <t>spoton</t>
+          <t>spot</t>
         </is>
       </c>
     </row>
@@ -8706,7 +8706,7 @@
       </c>
       <c r="P112" t="inlineStr">
         <is>
-          <t>spoton</t>
+          <t>spot</t>
         </is>
       </c>
     </row>

--- a/Tratamento/src/Dados_limpos/novos/limpo_petz_20260708_205654.xlsx
+++ b/Tratamento/src/Dados_limpos/novos/limpo_petz_20260708_205654.xlsx
@@ -5820,7 +5820,7 @@
       </c>
       <c r="P73" t="inlineStr">
         <is>
-          <t>plus</t>
+          <t>transdermal</t>
         </is>
       </c>
     </row>
@@ -6120,7 +6120,7 @@
       </c>
       <c r="P77" t="inlineStr">
         <is>
-          <t>plus</t>
+          <t>transdermal</t>
         </is>
       </c>
     </row>
@@ -6274,7 +6274,7 @@
       </c>
       <c r="P79" t="inlineStr">
         <is>
-          <t>plus</t>
+          <t>transdermal</t>
         </is>
       </c>
     </row>
@@ -8554,7 +8554,7 @@
       </c>
       <c r="P110" t="inlineStr">
         <is>
-          <t>spot</t>
+          <t>spoton</t>
         </is>
       </c>
     </row>
@@ -8630,7 +8630,7 @@
       </c>
       <c r="P111" t="inlineStr">
         <is>
-          <t>spot</t>
+          <t>spoton</t>
         </is>
       </c>
     </row>
@@ -8706,7 +8706,7 @@
       </c>
       <c r="P112" t="inlineStr">
         <is>
-          <t>spot</t>
+          <t>spoton</t>
         </is>
       </c>
     </row>

--- a/Tratamento/src/Dados_limpos/novos/limpo_petz_20260708_205654.xlsx
+++ b/Tratamento/src/Dados_limpos/novos/limpo_petz_20260708_205654.xlsx
@@ -5820,7 +5820,7 @@
       </c>
       <c r="P73" t="inlineStr">
         <is>
-          <t>transdermal</t>
+          <t>plus</t>
         </is>
       </c>
     </row>
@@ -6120,7 +6120,7 @@
       </c>
       <c r="P77" t="inlineStr">
         <is>
-          <t>transdermal</t>
+          <t>plus</t>
         </is>
       </c>
     </row>
@@ -6274,7 +6274,7 @@
       </c>
       <c r="P79" t="inlineStr">
         <is>
-          <t>transdermal</t>
+          <t>plus</t>
         </is>
       </c>
     </row>
@@ -6492,7 +6492,7 @@
       </c>
       <c r="P82" t="inlineStr">
         <is>
-          <t>topspot</t>
+          <t>spot</t>
         </is>
       </c>
     </row>
@@ -6566,7 +6566,7 @@
       </c>
       <c r="P83" t="inlineStr">
         <is>
-          <t>topspot</t>
+          <t>spot</t>
         </is>
       </c>
     </row>
@@ -7096,7 +7096,7 @@
       </c>
       <c r="P90" t="inlineStr">
         <is>
-          <t>topspot</t>
+          <t>spot</t>
         </is>
       </c>
     </row>
@@ -7170,7 +7170,7 @@
       </c>
       <c r="P91" t="inlineStr">
         <is>
-          <t>topspot</t>
+          <t>spot</t>
         </is>
       </c>
     </row>
@@ -8554,7 +8554,7 @@
       </c>
       <c r="P110" t="inlineStr">
         <is>
-          <t>spoton</t>
+          <t>spot</t>
         </is>
       </c>
     </row>
@@ -8630,7 +8630,7 @@
       </c>
       <c r="P111" t="inlineStr">
         <is>
-          <t>spoton</t>
+          <t>spot</t>
         </is>
       </c>
     </row>
@@ -8706,7 +8706,7 @@
       </c>
       <c r="P112" t="inlineStr">
         <is>
-          <t>spoton</t>
+          <t>spot</t>
         </is>
       </c>
     </row>

--- a/Tratamento/src/Dados_limpos/novos/limpo_petz_20260708_205654.xlsx
+++ b/Tratamento/src/Dados_limpos/novos/limpo_petz_20260708_205654.xlsx
@@ -5820,7 +5820,7 @@
       </c>
       <c r="P73" t="inlineStr">
         <is>
-          <t>plus</t>
+          <t>transdermal</t>
         </is>
       </c>
     </row>
@@ -6120,7 +6120,7 @@
       </c>
       <c r="P77" t="inlineStr">
         <is>
-          <t>plus</t>
+          <t>transdermal</t>
         </is>
       </c>
     </row>
@@ -6274,7 +6274,7 @@
       </c>
       <c r="P79" t="inlineStr">
         <is>
-          <t>plus</t>
+          <t>transdermal</t>
         </is>
       </c>
     </row>
@@ -6492,7 +6492,7 @@
       </c>
       <c r="P82" t="inlineStr">
         <is>
-          <t>topspot</t>
+          <t>spot</t>
         </is>
       </c>
     </row>
@@ -6566,7 +6566,7 @@
       </c>
       <c r="P83" t="inlineStr">
         <is>
-          <t>topspot</t>
+          <t>spot</t>
         </is>
       </c>
     </row>
@@ -7096,7 +7096,7 @@
       </c>
       <c r="P90" t="inlineStr">
         <is>
-          <t>topspot</t>
+          <t>spot</t>
         </is>
       </c>
     </row>
@@ -7170,7 +7170,7 @@
       </c>
       <c r="P91" t="inlineStr">
         <is>
-          <t>topspot</t>
+          <t>spot</t>
         </is>
       </c>
     </row>
@@ -8554,7 +8554,7 @@
       </c>
       <c r="P110" t="inlineStr">
         <is>
-          <t>spoton</t>
+          <t>spot</t>
         </is>
       </c>
     </row>
@@ -8630,7 +8630,7 @@
       </c>
       <c r="P111" t="inlineStr">
         <is>
-          <t>spoton</t>
+          <t>spot</t>
         </is>
       </c>
     </row>
@@ -8706,7 +8706,7 @@
       </c>
       <c r="P112" t="inlineStr">
         <is>
-          <t>spoton</t>
+          <t>spot</t>
         </is>
       </c>
     </row>

--- a/Tratamento/src/Dados_limpos/novos/limpo_petz_20260708_205654.xlsx
+++ b/Tratamento/src/Dados_limpos/novos/limpo_petz_20260708_205654.xlsx
@@ -8554,7 +8554,7 @@
       </c>
       <c r="P110" t="inlineStr">
         <is>
-          <t>spoton</t>
+          <t>spot</t>
         </is>
       </c>
     </row>
@@ -8630,7 +8630,7 @@
       </c>
       <c r="P111" t="inlineStr">
         <is>
-          <t>spoton</t>
+          <t>spot</t>
         </is>
       </c>
     </row>
@@ -8706,7 +8706,7 @@
       </c>
       <c r="P112" t="inlineStr">
         <is>
-          <t>spoton</t>
+          <t>spot</t>
         </is>
       </c>
     </row>

--- a/Tratamento/src/Dados_limpos/novos/limpo_petz_20260708_205654.xlsx
+++ b/Tratamento/src/Dados_limpos/novos/limpo_petz_20260708_205654.xlsx
@@ -5820,7 +5820,7 @@
       </c>
       <c r="P73" t="inlineStr">
         <is>
-          <t>plus</t>
+          <t>transdermal</t>
         </is>
       </c>
     </row>
@@ -6120,7 +6120,7 @@
       </c>
       <c r="P77" t="inlineStr">
         <is>
-          <t>plus</t>
+          <t>transdermal</t>
         </is>
       </c>
     </row>
@@ -6274,7 +6274,7 @@
       </c>
       <c r="P79" t="inlineStr">
         <is>
-          <t>plus</t>
+          <t>transdermal</t>
         </is>
       </c>
     </row>
@@ -6492,7 +6492,7 @@
       </c>
       <c r="P82" t="inlineStr">
         <is>
-          <t>spot</t>
+          <t>topspot</t>
         </is>
       </c>
     </row>
@@ -6566,7 +6566,7 @@
       </c>
       <c r="P83" t="inlineStr">
         <is>
-          <t>spot</t>
+          <t>topspot</t>
         </is>
       </c>
     </row>
@@ -7096,7 +7096,7 @@
       </c>
       <c r="P90" t="inlineStr">
         <is>
-          <t>spot</t>
+          <t>topspot</t>
         </is>
       </c>
     </row>
@@ -7170,7 +7170,7 @@
       </c>
       <c r="P91" t="inlineStr">
         <is>
-          <t>spot</t>
+          <t>topspot</t>
         </is>
       </c>
     </row>
@@ -8554,7 +8554,7 @@
       </c>
       <c r="P110" t="inlineStr">
         <is>
-          <t>spot</t>
+          <t>spoton</t>
         </is>
       </c>
     </row>
@@ -8630,7 +8630,7 @@
       </c>
       <c r="P111" t="inlineStr">
         <is>
-          <t>spot</t>
+          <t>spoton</t>
         </is>
       </c>
     </row>
@@ -8706,7 +8706,7 @@
       </c>
       <c r="P112" t="inlineStr">
         <is>
-          <t>spot</t>
+          <t>spoton</t>
         </is>
       </c>
     </row>

--- a/Tratamento/src/Dados_limpos/novos/limpo_petz_20260708_205654.xlsx
+++ b/Tratamento/src/Dados_limpos/novos/limpo_petz_20260708_205654.xlsx
@@ -5820,7 +5820,7 @@
       </c>
       <c r="P73" t="inlineStr">
         <is>
-          <t>transdermal</t>
+          <t>plus</t>
         </is>
       </c>
     </row>
@@ -6120,7 +6120,7 @@
       </c>
       <c r="P77" t="inlineStr">
         <is>
-          <t>transdermal</t>
+          <t>plus</t>
         </is>
       </c>
     </row>
@@ -6274,7 +6274,7 @@
       </c>
       <c r="P79" t="inlineStr">
         <is>
-          <t>transdermal</t>
+          <t>plus</t>
         </is>
       </c>
     </row>
@@ -6492,7 +6492,7 @@
       </c>
       <c r="P82" t="inlineStr">
         <is>
-          <t>topspot</t>
+          <t>spot</t>
         </is>
       </c>
     </row>
@@ -6566,7 +6566,7 @@
       </c>
       <c r="P83" t="inlineStr">
         <is>
-          <t>topspot</t>
+          <t>spot</t>
         </is>
       </c>
     </row>
@@ -7096,7 +7096,7 @@
       </c>
       <c r="P90" t="inlineStr">
         <is>
-          <t>topspot</t>
+          <t>spot</t>
         </is>
       </c>
     </row>
@@ -7170,7 +7170,7 @@
       </c>
       <c r="P91" t="inlineStr">
         <is>
-          <t>topspot</t>
+          <t>spot</t>
         </is>
       </c>
     </row>

--- a/Tratamento/src/Dados_limpos/novos/limpo_petz_20260708_205654.xlsx
+++ b/Tratamento/src/Dados_limpos/novos/limpo_petz_20260708_205654.xlsx
@@ -5820,7 +5820,7 @@
       </c>
       <c r="P73" t="inlineStr">
         <is>
-          <t>plus</t>
+          <t>transdermal</t>
         </is>
       </c>
     </row>
@@ -6120,7 +6120,7 @@
       </c>
       <c r="P77" t="inlineStr">
         <is>
-          <t>plus</t>
+          <t>transdermal</t>
         </is>
       </c>
     </row>
@@ -6274,7 +6274,7 @@
       </c>
       <c r="P79" t="inlineStr">
         <is>
-          <t>plus</t>
+          <t>transdermal</t>
         </is>
       </c>
     </row>
@@ -6492,7 +6492,7 @@
       </c>
       <c r="P82" t="inlineStr">
         <is>
-          <t>spot</t>
+          <t>topspot</t>
         </is>
       </c>
     </row>
@@ -6566,7 +6566,7 @@
       </c>
       <c r="P83" t="inlineStr">
         <is>
-          <t>spot</t>
+          <t>topspot</t>
         </is>
       </c>
     </row>
@@ -7096,7 +7096,7 @@
       </c>
       <c r="P90" t="inlineStr">
         <is>
-          <t>spot</t>
+          <t>topspot</t>
         </is>
       </c>
     </row>
@@ -7170,7 +7170,7 @@
       </c>
       <c r="P91" t="inlineStr">
         <is>
-          <t>spot</t>
+          <t>topspot</t>
         </is>
       </c>
     </row>
